--- a/data/trans_orig/P57C2_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P57C2_2023-Habitat-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si se ha sentido bien consigo mismo/a en 2023</t>
+          <t>Población según si se ha sentido bien consigo mismo/a en 2023 (tasa de respuesta: 99,79%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6247</t>
+          <t>6220</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>21432</t>
+          <t>22004</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -750,7 +750,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>8118</t>
+          <t>8384</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>20650</t>
+          <t>19561</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>17528</t>
+          <t>16402</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>36191</t>
+          <t>35315</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,7%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>15580</t>
+          <t>16377</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>32639</t>
+          <t>33537</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>25516</t>
+          <t>24333</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>40979</t>
+          <t>40594</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>44964</t>
+          <t>45187</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>69800</t>
+          <t>69663</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,32%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>47795</t>
+          <t>47932</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>74829</t>
+          <t>75698</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>7,55%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>11,79%</t>
+          <t>11,92%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>76354</t>
+          <t>78027</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>102151</t>
+          <t>103434</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>11,33%</t>
+          <t>11,57%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>15,15%</t>
+          <t>15,34%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>131782</t>
+          <t>132302</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>170722</t>
+          <t>169434</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>10,11%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>13,04%</t>
+          <t>12,94%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>258805</t>
+          <t>261458</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>314020</t>
+          <t>314816</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>40,77%</t>
+          <t>41,18%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>49,46%</t>
+          <t>49,59%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>303630</t>
+          <t>303152</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>346116</t>
+          <t>345928</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>45,04%</t>
+          <t>44,97%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>51,34%</t>
+          <t>51,31%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>574853</t>
+          <t>577922</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>645656</t>
+          <t>650414</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>43,92%</t>
+          <t>44,15%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>49,32%</t>
+          <t>49,69%</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>225118</t>
+          <t>225784</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>281920</t>
+          <t>278853</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1197,12 +1197,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>35,46%</t>
+          <t>35,56%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>44,41%</t>
+          <t>43,92%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1217,12 +1217,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>194858</t>
+          <t>193514</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>234045</t>
+          <t>235521</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1232,12 +1232,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>28,9%</t>
+          <t>28,71%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>34,72%</t>
+          <t>34,94%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1252,12 +1252,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>433464</t>
+          <t>434068</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>503740</t>
+          <t>503123</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1267,12 +1267,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>33,11%</t>
+          <t>33,16%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>38,48%</t>
+          <t>38,44%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3828</t>
+          <t>4028</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>19905</t>
+          <t>20452</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>8380</t>
+          <t>8233</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>25418</t>
+          <t>25124</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>14511</t>
+          <t>14935</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>38685</t>
+          <t>39599</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,84%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>12579</t>
+          <t>12883</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>38835</t>
+          <t>39082</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>35160</t>
+          <t>34017</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>56102</t>
+          <t>55847</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>48227</t>
+          <t>44532</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>86173</t>
+          <t>85559</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>3,98%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>46281</t>
+          <t>43425</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>118035</t>
+          <t>117353</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>9,84%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>101665</t>
+          <t>101702</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>134060</t>
+          <t>134440</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1693,7 +1693,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>14,03%</t>
+          <t>14,07%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>133444</t>
+          <t>133981</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>238817</t>
+          <t>240674</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>11,11%</t>
+          <t>11,2%</t>
         </is>
       </c>
     </row>
@@ -1751,12 +1751,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>232186</t>
+          <t>204156</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>548901</t>
+          <t>540927</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1766,12 +1766,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>19,46%</t>
+          <t>17,11%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>46,02%</t>
+          <t>45,35%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1786,12 +1786,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>415454</t>
+          <t>418868</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>468358</t>
+          <t>472255</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1801,12 +1801,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>43,47%</t>
+          <t>43,82%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>49,0%</t>
+          <t>49,41%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1821,12 +1821,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>588193</t>
+          <t>577945</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>991816</t>
+          <t>993210</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>27,37%</t>
+          <t>26,9%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>46,16%</t>
+          <t>46,22%</t>
         </is>
       </c>
     </row>
@@ -1864,12 +1864,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>494858</t>
+          <t>498472</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>892624</t>
+          <t>934479</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1879,12 +1879,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>41,48%</t>
+          <t>41,79%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>74,83%</t>
+          <t>78,34%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1899,12 +1899,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>309709</t>
+          <t>309157</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>364673</t>
+          <t>361436</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1914,12 +1914,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>32,4%</t>
+          <t>32,35%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>38,15%</t>
+          <t>37,81%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1934,12 +1934,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>822604</t>
+          <t>816189</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1346742</t>
+          <t>1369275</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1949,12 +1949,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>38,28%</t>
+          <t>37,99%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>62,68%</t>
+          <t>63,73%</t>
         </is>
       </c>
     </row>
@@ -2094,12 +2094,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2636</t>
+          <t>2771</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>15329</t>
+          <t>14666</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2109,12 +2109,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2129,12 +2129,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2545</t>
+          <t>2429</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>18380</t>
+          <t>19502</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2144,12 +2144,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2164,12 +2164,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>7121</t>
+          <t>7230</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>27695</t>
+          <t>26813</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2184,7 +2184,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,64%</t>
         </is>
       </c>
     </row>
@@ -2207,12 +2207,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>7924</t>
+          <t>7099</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>22616</t>
+          <t>22132</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2222,12 +2222,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>7099</t>
+          <t>7038</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>24735</t>
+          <t>24843</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2262,7 +2262,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>18211</t>
+          <t>17329</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>41254</t>
+          <t>40592</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2292,12 +2292,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,48%</t>
         </is>
       </c>
     </row>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>30470</t>
+          <t>30842</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>58543</t>
+          <t>59034</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2335,12 +2335,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>8,32%</t>
+          <t>8,39%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2355,12 +2355,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>28042</t>
+          <t>27409</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>79221</t>
+          <t>79716</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2370,12 +2370,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>8,57%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2390,12 +2390,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>65718</t>
+          <t>59630</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>122116</t>
+          <t>122260</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2405,12 +2405,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>7,48%</t>
         </is>
       </c>
     </row>
@@ -2433,12 +2433,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>325404</t>
+          <t>325288</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>385708</t>
+          <t>387810</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2448,12 +2448,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>46,24%</t>
+          <t>46,23%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>54,81%</t>
+          <t>55,11%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2468,12 +2468,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>487671</t>
+          <t>487716</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>758907</t>
+          <t>750447</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2488,7 +2488,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>81,57%</t>
+          <t>80,66%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2503,12 +2503,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>841837</t>
+          <t>837734</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>1206269</t>
+          <t>1203072</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>51,52%</t>
+          <t>51,27%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>73,82%</t>
+          <t>73,62%</t>
         </is>
       </c>
     </row>
@@ -2546,12 +2546,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>255830</t>
+          <t>256202</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>314082</t>
+          <t>319355</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2561,12 +2561,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>36,36%</t>
+          <t>36,41%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>44,63%</t>
+          <t>45,38%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2581,12 +2581,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>130869</t>
+          <t>133038</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>338917</t>
+          <t>335314</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>14,07%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>36,43%</t>
+          <t>36,04%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2616,12 +2616,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>346806</t>
+          <t>344592</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>630236</t>
+          <t>635726</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>21,22%</t>
+          <t>21,09%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>38,57%</t>
+          <t>38,9%</t>
         </is>
       </c>
     </row>
@@ -2776,12 +2776,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>4629</t>
+          <t>4811</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>16293</t>
+          <t>16841</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>6510</t>
+          <t>6909</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>17014</t>
+          <t>17035</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2826,7 +2826,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>13478</t>
+          <t>14046</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>30948</t>
+          <t>30423</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,51%</t>
         </is>
       </c>
     </row>
@@ -2889,12 +2889,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>21637</t>
+          <t>23177</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>43597</t>
+          <t>45025</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2904,12 +2904,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2924,12 +2924,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>39648</t>
+          <t>39064</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>66243</t>
+          <t>65580</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2959,12 +2959,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>67643</t>
+          <t>67919</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>102408</t>
+          <t>102816</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>5,1%</t>
         </is>
       </c>
     </row>
@@ -3002,12 +3002,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>73448</t>
+          <t>71135</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>108581</t>
+          <t>108112</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3017,12 +3017,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>7,69%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>11,74%</t>
+          <t>11,69%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>95348</t>
+          <t>97598</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>143859</t>
+          <t>143082</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3052,12 +3052,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>8,93%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>13,16%</t>
+          <t>13,09%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>178500</t>
+          <t>179006</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>239103</t>
+          <t>239364</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3087,12 +3087,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>8,87%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>11,85%</t>
+          <t>11,86%</t>
         </is>
       </c>
     </row>
@@ -3115,12 +3115,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>397589</t>
+          <t>399901</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>463420</t>
+          <t>463769</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3130,12 +3130,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>43,0%</t>
+          <t>43,25%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>50,12%</t>
+          <t>50,16%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>379869</t>
+          <t>371876</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>511130</t>
+          <t>508893</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3165,12 +3165,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>34,75%</t>
+          <t>34,02%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>46,76%</t>
+          <t>46,56%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>797580</t>
+          <t>792923</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>954323</t>
+          <t>952339</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3200,12 +3200,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>39,53%</t>
+          <t>39,3%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>47,3%</t>
+          <t>47,2%</t>
         </is>
       </c>
     </row>
@@ -3228,12 +3228,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>334538</t>
+          <t>333422</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>394797</t>
+          <t>397020</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3243,12 +3243,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>36,18%</t>
+          <t>36,06%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>42,7%</t>
+          <t>42,94%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3263,12 +3263,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>385019</t>
+          <t>385597</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>559804</t>
+          <t>557851</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3278,12 +3278,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>35,22%</t>
+          <t>35,28%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>51,21%</t>
+          <t>51,03%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3298,12 +3298,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>739877</t>
+          <t>743999</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>956973</t>
+          <t>962792</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3313,12 +3313,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>36,67%</t>
+          <t>36,87%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>47,43%</t>
+          <t>47,72%</t>
         </is>
       </c>
     </row>
@@ -3458,12 +3458,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>26604</t>
+          <t>27127</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>54883</t>
+          <t>55726</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3473,12 +3473,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>33102</t>
+          <t>34734</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>61712</t>
+          <t>62830</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3508,12 +3508,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>66397</t>
+          <t>68869</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>106374</t>
+          <t>107934</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3543,12 +3543,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,52%</t>
         </is>
       </c>
     </row>
@@ -3571,12 +3571,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>72639</t>
+          <t>70990</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>116190</t>
+          <t>113087</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3586,12 +3586,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3606,12 +3606,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>117397</t>
+          <t>117838</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>168718</t>
+          <t>169300</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3621,12 +3621,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3641,12 +3641,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>199827</t>
+          <t>199289</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>266420</t>
+          <t>268386</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3656,12 +3656,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,78%</t>
         </is>
       </c>
     </row>
@@ -3684,12 +3684,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>216855</t>
+          <t>218882</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>316633</t>
+          <t>317770</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3699,12 +3699,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>9,19%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3719,12 +3719,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>316667</t>
+          <t>312078</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>427922</t>
+          <t>427172</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3734,12 +3734,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>8,54%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>11,71%</t>
+          <t>11,69%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3754,12 +3754,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>574294</t>
+          <t>574616</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>723130</t>
+          <t>724636</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3774,7 +3774,7 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>10,19%</t>
         </is>
       </c>
     </row>
@@ -3797,12 +3797,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>1155429</t>
+          <t>1135032</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>1638418</t>
+          <t>1636233</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3812,12 +3812,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>33,43%</t>
+          <t>32,84%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>47,41%</t>
+          <t>47,35%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3832,12 +3832,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>1693005</t>
+          <t>1696913</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>2132488</t>
+          <t>2165482</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3847,12 +3847,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>46,34%</t>
+          <t>46,45%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>58,37%</t>
+          <t>59,27%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3867,12 +3867,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>3023131</t>
+          <t>3023394</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>3635967</t>
+          <t>3656725</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3882,12 +3882,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>42,52%</t>
+          <t>42,53%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>51,14%</t>
+          <t>51,44%</t>
         </is>
       </c>
     </row>
@@ -3910,12 +3910,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>1380322</t>
+          <t>1379554</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>1975948</t>
+          <t>2002004</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3925,12 +3925,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>39,94%</t>
+          <t>39,92%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>57,18%</t>
+          <t>57,93%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3945,12 +3945,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>1044372</t>
+          <t>1055393</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>1370878</t>
+          <t>1382655</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3960,12 +3960,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>28,59%</t>
+          <t>28,89%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>37,52%</t>
+          <t>37,85%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3980,12 +3980,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>2543893</t>
+          <t>2528757</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>3260406</t>
+          <t>3237245</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3995,12 +3995,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>35,78%</t>
+          <t>35,57%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>45,86%</t>
+          <t>45,54%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P57C2_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P57C2_2023-Habitat-trans_orig.xlsx
@@ -725,102 +725,102 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>12362</t>
+          <t>13700</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6220</t>
+          <t>7390</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>22004</t>
+          <t>24470</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
+          <t>1,99%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>1,07%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>3,55%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>14052</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>8993</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>21121</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>1,92%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>1,23%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>2,89%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>27752</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>18731</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>40727</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
           <t>1,95%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0,98%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>3,47%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>12879</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>8384</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>19561</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>1,91%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>1,24%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>2,9%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>25240</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>16402</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>35315</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>1,93%</t>
-        </is>
-      </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,87%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>23408</t>
+          <t>25292</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>16377</t>
+          <t>16686</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>33537</t>
+          <t>36566</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>32212</t>
+          <t>34915</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>24333</t>
+          <t>26474</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>40594</t>
+          <t>43612</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>55619</t>
+          <t>60207</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>45187</t>
+          <t>48145</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>69663</t>
+          <t>73840</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,19%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>60409</t>
+          <t>67349</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>47932</t>
+          <t>53653</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>75698</t>
+          <t>85573</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>9,76%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>11,92%</t>
+          <t>12,4%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>89726</t>
+          <t>99293</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>78027</t>
+          <t>85784</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>103434</t>
+          <t>115585</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>13,31%</t>
+          <t>13,57%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>11,57%</t>
+          <t>11,73%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>15,34%</t>
+          <t>15,8%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>150135</t>
+          <t>166642</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>132302</t>
+          <t>147259</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>169434</t>
+          <t>187912</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>11,72%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>10,11%</t>
+          <t>10,36%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>12,94%</t>
+          <t>13,22%</t>
         </is>
       </c>
     </row>
@@ -1064,32 +1064,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>287943</t>
+          <t>308180</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>261458</t>
+          <t>280285</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>314816</t>
+          <t>336473</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>45,36%</t>
+          <t>44,66%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>41,18%</t>
+          <t>40,62%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>49,59%</t>
+          <t>48,76%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>324853</t>
+          <t>345820</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>303152</t>
+          <t>324571</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>345928</t>
+          <t>370860</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>48,19%</t>
+          <t>47,28%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>44,97%</t>
+          <t>44,37%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>51,31%</t>
+          <t>50,7%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>612795</t>
+          <t>654000</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>577922</t>
+          <t>619595</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>650414</t>
+          <t>691562</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>46,81%</t>
+          <t>46,01%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>44,15%</t>
+          <t>43,59%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>49,69%</t>
+          <t>48,65%</t>
         </is>
       </c>
     </row>
@@ -1177,32 +1177,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>250727</t>
+          <t>275517</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>225784</t>
+          <t>247951</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>278853</t>
+          <t>303945</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>39,49%</t>
+          <t>39,93%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>35,56%</t>
+          <t>35,93%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>43,92%</t>
+          <t>44,05%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1212,32 +1212,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>214471</t>
+          <t>237399</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>193514</t>
+          <t>213102</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>235521</t>
+          <t>259108</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>31,81%</t>
+          <t>32,45%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>28,71%</t>
+          <t>29,13%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>34,94%</t>
+          <t>35,42%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1247,32 +1247,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>465199</t>
+          <t>512916</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>434068</t>
+          <t>477819</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>503123</t>
+          <t>552831</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>35,54%</t>
+          <t>36,08%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>33,16%</t>
+          <t>33,61%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>38,44%</t>
+          <t>38,89%</t>
         </is>
       </c>
     </row>
@@ -1290,17 +1290,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>634848</t>
+          <t>690038</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>634848</t>
+          <t>690038</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>634848</t>
+          <t>690038</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1325,17 +1325,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>674140</t>
+          <t>731478</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>674140</t>
+          <t>731478</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>674140</t>
+          <t>731478</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1360,17 +1360,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1308988</t>
+          <t>1421516</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1308988</t>
+          <t>1421516</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1308988</t>
+          <t>1421516</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>10930</t>
+          <t>11561</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4028</t>
+          <t>5614</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>20452</t>
+          <t>21530</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>14023</t>
+          <t>15596</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>8233</t>
+          <t>9483</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>25124</t>
+          <t>27959</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>24952</t>
+          <t>27157</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>14935</t>
+          <t>18810</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>39599</t>
+          <t>45770</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>2,16%</t>
         </is>
       </c>
     </row>
@@ -1520,32 +1520,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>24316</t>
+          <t>28180</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>12883</t>
+          <t>19368</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>39082</t>
+          <t>42424</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1555,67 +1555,67 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>44061</t>
+          <t>50715</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>34017</t>
+          <t>39746</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>55847</t>
+          <t>63909</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
+          <t>4,75%</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>3,72%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>5,98%</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>78895</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>64385</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>97526</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>3,73%</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>3,04%</t>
+        </is>
+      </c>
+      <c r="W11" s="2" t="inlineStr">
+        <is>
           <t>4,61%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>3,56%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>5,84%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>109</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>68376</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>44532</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>85559</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>3,18%</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>2,07%</t>
-        </is>
-      </c>
-      <c r="W11" s="2" t="inlineStr">
-        <is>
-          <t>3,98%</t>
         </is>
       </c>
     </row>
@@ -1633,32 +1633,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>86500</t>
+          <t>98862</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>43425</t>
+          <t>80641</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>117353</t>
+          <t>119171</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>9,43%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>7,69%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>11,36%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1668,32 +1668,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>117273</t>
+          <t>131429</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>101702</t>
+          <t>115230</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>134440</t>
+          <t>148656</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>12,27%</t>
+          <t>12,3%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>10,64%</t>
+          <t>10,79%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>14,07%</t>
+          <t>13,91%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>203773</t>
+          <t>230291</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>133981</t>
+          <t>204957</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>240674</t>
+          <t>258719</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>10,88%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>9,68%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>12,22%</t>
         </is>
       </c>
     </row>
@@ -1746,32 +1746,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>422962</t>
+          <t>454988</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>204156</t>
+          <t>421418</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>540927</t>
+          <t>491807</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>35,46%</t>
+          <t>43,38%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>17,11%</t>
+          <t>40,18%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>45,35%</t>
+          <t>46,89%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1781,32 +1781,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>444169</t>
+          <t>496131</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>418868</t>
+          <t>466661</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>472255</t>
+          <t>526248</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>46,47%</t>
+          <t>46,44%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>43,82%</t>
+          <t>43,68%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>49,41%</t>
+          <t>49,26%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1816,32 +1816,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>867131</t>
+          <t>951119</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>577945</t>
+          <t>907272</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>993210</t>
+          <t>994497</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>40,36%</t>
+          <t>44,92%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>26,9%</t>
+          <t>42,85%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>46,22%</t>
+          <t>46,97%</t>
         </is>
       </c>
     </row>
@@ -1859,32 +1859,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>648157</t>
+          <t>455325</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>498472</t>
+          <t>421402</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>934479</t>
+          <t>490976</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>54,34%</t>
+          <t>43,41%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>41,79%</t>
+          <t>40,17%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>78,34%</t>
+          <t>46,81%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1894,32 +1894,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>336277</t>
+          <t>374517</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>309157</t>
+          <t>346251</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>361436</t>
+          <t>403457</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>35,18%</t>
+          <t>35,05%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>32,35%</t>
+          <t>32,41%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>37,81%</t>
+          <t>37,76%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1929,32 +1929,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>984435</t>
+          <t>829843</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>816189</t>
+          <t>781662</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1369275</t>
+          <t>875454</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>45,82%</t>
+          <t>39,19%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>37,99%</t>
+          <t>36,92%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>63,73%</t>
+          <t>41,35%</t>
         </is>
       </c>
     </row>
@@ -1972,17 +1972,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2007,17 +2007,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>955803</t>
+          <t>1068388</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>955803</t>
+          <t>1068388</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>955803</t>
+          <t>1068388</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2042,17 +2042,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2148667</t>
+          <t>2117305</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2148667</t>
+          <t>2117305</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2148667</t>
+          <t>2117305</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2089,32 +2089,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>6814</t>
+          <t>7253</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2771</t>
+          <t>2603</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>14666</t>
+          <t>16069</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2124,32 +2124,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>8261</t>
+          <t>9962</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2429</t>
+          <t>4252</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>19502</t>
+          <t>21034</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>15075</t>
+          <t>17215</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>7230</t>
+          <t>9587</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>26813</t>
+          <t>31063</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,93%</t>
         </is>
       </c>
     </row>
@@ -2202,32 +2202,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>13106</t>
+          <t>14071</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>7099</t>
+          <t>7815</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>22132</t>
+          <t>23386</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>15766</t>
+          <t>20737</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>7038</t>
+          <t>13997</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>24843</t>
+          <t>33813</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>28872</t>
+          <t>34808</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>17329</t>
+          <t>24862</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>40592</t>
+          <t>49494</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>3,07%</t>
         </is>
       </c>
     </row>
@@ -2315,32 +2315,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>41952</t>
+          <t>50298</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>30842</t>
+          <t>37330</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>59034</t>
+          <t>69089</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>8,61%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2350,32 +2350,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>56011</t>
+          <t>61972</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>27409</t>
+          <t>51076</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>79716</t>
+          <t>76779</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>9,49%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2385,32 +2385,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>97963</t>
+          <t>112269</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>59630</t>
+          <t>94135</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>122260</t>
+          <t>137630</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>6,97%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>8,54%</t>
         </is>
       </c>
     </row>
@@ -2428,32 +2428,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>356928</t>
+          <t>399731</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>325288</t>
+          <t>366938</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>387810</t>
+          <t>433031</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>50,72%</t>
+          <t>49,84%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>46,23%</t>
+          <t>45,75%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>55,11%</t>
+          <t>53,99%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2463,32 +2463,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>598857</t>
+          <t>415082</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>487716</t>
+          <t>388099</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>750447</t>
+          <t>441693</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>64,37%</t>
+          <t>51,3%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>52,42%</t>
+          <t>47,96%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>80,66%</t>
+          <t>54,59%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2498,32 +2498,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>955784</t>
+          <t>814813</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>837734</t>
+          <t>771164</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>1203072</t>
+          <t>854340</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>58,49%</t>
+          <t>50,57%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>51,27%</t>
+          <t>47,86%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>73,62%</t>
+          <t>53,02%</t>
         </is>
       </c>
     </row>
@@ -2541,32 +2541,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>284884</t>
+          <t>330733</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>256202</t>
+          <t>296609</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>319355</t>
+          <t>363778</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>40,48%</t>
+          <t>41,23%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>36,41%</t>
+          <t>36,98%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>45,38%</t>
+          <t>45,35%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2576,32 +2576,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>251475</t>
+          <t>301397</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>133038</t>
+          <t>274449</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>335314</t>
+          <t>326291</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>27,03%</t>
+          <t>37,25%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>33,92%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>36,04%</t>
+          <t>40,33%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2611,32 +2611,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>536360</t>
+          <t>632130</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>344592</t>
+          <t>589880</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>635726</t>
+          <t>675198</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>32,82%</t>
+          <t>39,23%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>21,09%</t>
+          <t>36,61%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>38,9%</t>
+          <t>41,91%</t>
         </is>
       </c>
     </row>
@@ -2654,17 +2654,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>703684</t>
+          <t>802086</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>703684</t>
+          <t>802086</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>703684</t>
+          <t>802086</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2689,17 +2689,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>930370</t>
+          <t>809149</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>930370</t>
+          <t>809149</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>930370</t>
+          <t>809149</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2724,17 +2724,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>1634054</t>
+          <t>1611235</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1634054</t>
+          <t>1611235</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1634054</t>
+          <t>1611235</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2771,32 +2771,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>9306</t>
+          <t>10529</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>4811</t>
+          <t>5496</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>16841</t>
+          <t>19435</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>11122</t>
+          <t>11898</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>6909</t>
+          <t>7390</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>17035</t>
+          <t>18241</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>20428</t>
+          <t>22427</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>14046</t>
+          <t>14874</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>30423</t>
+          <t>31318</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,49%</t>
         </is>
       </c>
     </row>
@@ -2884,102 +2884,102 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>32529</t>
+          <t>32834</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>23177</t>
+          <t>22661</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>45025</t>
+          <t>44609</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
+          <t>3,32%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>2,29%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>4,52%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>57826</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>46500</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>70740</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>5,18%</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>4,16%</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>6,33%</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr">
+        <is>
+          <t>90660</t>
+        </is>
+      </c>
+      <c r="S23" s="2" t="inlineStr">
+        <is>
+          <t>74089</t>
+        </is>
+      </c>
+      <c r="T23" s="2" t="inlineStr">
+        <is>
+          <t>109197</t>
+        </is>
+      </c>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
+          <t>4,31%</t>
+        </is>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
           <t>3,52%</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>2,51%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>4,87%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>51669</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>39064</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>65580</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>4,73%</t>
-        </is>
-      </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>3,57%</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>6,0%</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>123</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t>84197</t>
-        </is>
-      </c>
-      <c r="S23" s="2" t="inlineStr">
-        <is>
-          <t>67919</t>
-        </is>
-      </c>
-      <c r="T23" s="2" t="inlineStr">
-        <is>
-          <t>102816</t>
-        </is>
-      </c>
-      <c r="U23" s="2" t="inlineStr">
-        <is>
-          <t>4,17%</t>
-        </is>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>3,37%</t>
-        </is>
-      </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>5,19%</t>
         </is>
       </c>
     </row>
@@ -2997,32 +2997,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>88005</t>
+          <t>93296</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>71135</t>
+          <t>76507</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>108112</t>
+          <t>113099</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>9,44%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>7,74%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>11,69%</t>
+          <t>11,45%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3032,32 +3032,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>122753</t>
+          <t>136718</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>97598</t>
+          <t>117562</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>143082</t>
+          <t>155909</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>11,23%</t>
+          <t>12,24%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>10,52%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>13,09%</t>
+          <t>13,96%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3067,32 +3067,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>210758</t>
+          <t>230014</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>179006</t>
+          <t>204162</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>239364</t>
+          <t>259948</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>10,45%</t>
+          <t>10,93%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>9,7%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>11,86%</t>
+          <t>12,35%</t>
         </is>
       </c>
     </row>
@@ -3110,32 +3110,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>430966</t>
+          <t>452169</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>399901</t>
+          <t>420845</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>463769</t>
+          <t>484778</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>46,61%</t>
+          <t>45,77%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>43,25%</t>
+          <t>42,6%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>50,16%</t>
+          <t>49,07%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3145,32 +3145,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>467706</t>
+          <t>505731</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>371876</t>
+          <t>473958</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>508893</t>
+          <t>534472</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>42,79%</t>
+          <t>45,27%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>34,02%</t>
+          <t>42,43%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>46,56%</t>
+          <t>47,84%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3180,32 +3180,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>898672</t>
+          <t>957900</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>792923</t>
+          <t>916405</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>952339</t>
+          <t>1002248</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>44,54%</t>
+          <t>45,5%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>39,3%</t>
+          <t>43,53%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>47,2%</t>
+          <t>47,61%</t>
         </is>
       </c>
     </row>
@@ -3223,32 +3223,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>363753</t>
+          <t>399090</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>333422</t>
+          <t>366895</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>397020</t>
+          <t>431531</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>39,34%</t>
+          <t>40,4%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>36,06%</t>
+          <t>37,14%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>42,94%</t>
+          <t>43,68%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3258,32 +3258,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>439838</t>
+          <t>404967</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>385597</t>
+          <t>375937</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>557851</t>
+          <t>433754</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>40,24%</t>
+          <t>36,25%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>35,28%</t>
+          <t>33,65%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>51,03%</t>
+          <t>38,83%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3293,32 +3293,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>803592</t>
+          <t>804057</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>743999</t>
+          <t>763080</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>962792</t>
+          <t>851537</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>39,83%</t>
+          <t>38,2%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>36,87%</t>
+          <t>36,25%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>47,72%</t>
+          <t>40,45%</t>
         </is>
       </c>
     </row>
@@ -3336,17 +3336,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>924558</t>
+          <t>987918</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>924558</t>
+          <t>987918</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>924558</t>
+          <t>987918</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3371,17 +3371,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>1093088</t>
+          <t>1117140</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>1093088</t>
+          <t>1117140</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>1093088</t>
+          <t>1117140</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3406,17 +3406,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>2017647</t>
+          <t>2105057</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>2017647</t>
+          <t>2105057</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>2017647</t>
+          <t>2105057</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3453,102 +3453,102 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>39411</t>
+          <t>43043</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>27127</t>
+          <t>30403</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>55726</t>
+          <t>58773</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
+          <t>1,67%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>51507</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>38823</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>67059</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>1,38%</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>1,04%</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>1,8%</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="R28" s="2" t="inlineStr">
+        <is>
+          <t>94551</t>
+        </is>
+      </c>
+      <c r="S28" s="2" t="inlineStr">
+        <is>
+          <t>75345</t>
+        </is>
+      </c>
+      <c r="T28" s="2" t="inlineStr">
+        <is>
+          <t>116989</t>
+        </is>
+      </c>
+      <c r="U28" s="2" t="inlineStr">
+        <is>
+          <t>1,3%</t>
+        </is>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
+          <t>1,04%</t>
+        </is>
+      </c>
+      <c r="W28" s="2" t="inlineStr">
+        <is>
           <t>1,61%</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>69</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t>46285</t>
-        </is>
-      </c>
-      <c r="L28" s="2" t="inlineStr">
-        <is>
-          <t>34734</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr">
-        <is>
-          <t>62830</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr">
-        <is>
-          <t>1,27%</t>
-        </is>
-      </c>
-      <c r="O28" s="2" t="inlineStr">
-        <is>
-          <t>0,95%</t>
-        </is>
-      </c>
-      <c r="P28" s="2" t="inlineStr">
-        <is>
-          <t>1,72%</t>
-        </is>
-      </c>
-      <c r="Q28" s="2" t="inlineStr">
-        <is>
-          <t>109</t>
-        </is>
-      </c>
-      <c r="R28" s="2" t="inlineStr">
-        <is>
-          <t>85695</t>
-        </is>
-      </c>
-      <c r="S28" s="2" t="inlineStr">
-        <is>
-          <t>68869</t>
-        </is>
-      </c>
-      <c r="T28" s="2" t="inlineStr">
-        <is>
-          <t>107934</t>
-        </is>
-      </c>
-      <c r="U28" s="2" t="inlineStr">
-        <is>
-          <t>1,21%</t>
-        </is>
-      </c>
-      <c r="V28" s="2" t="inlineStr">
-        <is>
-          <t>0,97%</t>
-        </is>
-      </c>
-      <c r="W28" s="2" t="inlineStr">
-        <is>
-          <t>1,52%</t>
         </is>
       </c>
     </row>
@@ -3566,102 +3566,102 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>93358</t>
+          <t>100378</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>70990</t>
+          <t>82025</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>113087</t>
+          <t>120209</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
+          <t>3,41%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>164192</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>143807</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>186952</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>4,41%</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>3,86%</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>5,02%</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr">
+        <is>
+          <t>364</t>
+        </is>
+      </c>
+      <c r="R29" s="2" t="inlineStr">
+        <is>
+          <t>264570</t>
+        </is>
+      </c>
+      <c r="S29" s="2" t="inlineStr">
+        <is>
+          <t>237487</t>
+        </is>
+      </c>
+      <c r="T29" s="2" t="inlineStr">
+        <is>
+          <t>298730</t>
+        </is>
+      </c>
+      <c r="U29" s="2" t="inlineStr">
+        <is>
+          <t>3,65%</t>
+        </is>
+      </c>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
           <t>3,27%</t>
         </is>
       </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>250</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>143707</t>
-        </is>
-      </c>
-      <c r="L29" s="2" t="inlineStr">
-        <is>
-          <t>117838</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="inlineStr">
-        <is>
-          <t>169300</t>
-        </is>
-      </c>
-      <c r="N29" s="2" t="inlineStr">
-        <is>
-          <t>3,93%</t>
-        </is>
-      </c>
-      <c r="O29" s="2" t="inlineStr">
-        <is>
-          <t>3,23%</t>
-        </is>
-      </c>
-      <c r="P29" s="2" t="inlineStr">
-        <is>
-          <t>4,63%</t>
-        </is>
-      </c>
-      <c r="Q29" s="2" t="inlineStr">
-        <is>
-          <t>364</t>
-        </is>
-      </c>
-      <c r="R29" s="2" t="inlineStr">
-        <is>
-          <t>237065</t>
-        </is>
-      </c>
-      <c r="S29" s="2" t="inlineStr">
-        <is>
-          <t>199289</t>
-        </is>
-      </c>
-      <c r="T29" s="2" t="inlineStr">
-        <is>
-          <t>268386</t>
-        </is>
-      </c>
-      <c r="U29" s="2" t="inlineStr">
-        <is>
-          <t>3,33%</t>
-        </is>
-      </c>
-      <c r="V29" s="2" t="inlineStr">
-        <is>
-          <t>2,8%</t>
-        </is>
-      </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>4,12%</t>
         </is>
       </c>
     </row>
@@ -3679,32 +3679,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>276865</t>
+          <t>309805</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>218882</t>
+          <t>278281</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>317770</t>
+          <t>344022</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>8,78%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>7,89%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>9,19%</t>
+          <t>9,75%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3714,32 +3714,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>385763</t>
+          <t>429411</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>312078</t>
+          <t>394201</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>427172</t>
+          <t>459904</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>11,52%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>10,58%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>11,69%</t>
+          <t>12,34%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3749,32 +3749,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>662629</t>
+          <t>739216</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>574616</t>
+          <t>693846</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>724636</t>
+          <t>788008</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>10,19%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>9,56%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>10,86%</t>
         </is>
       </c>
     </row>
@@ -3792,32 +3792,32 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>1498798</t>
+          <t>1615067</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>1135032</t>
+          <t>1550733</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>1636233</t>
+          <t>1684908</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>43,37%</t>
+          <t>45,77%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>32,84%</t>
+          <t>43,94%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>47,35%</t>
+          <t>47,75%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3827,32 +3827,32 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>1835584</t>
+          <t>1762765</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>1696913</t>
+          <t>1707913</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>2165482</t>
+          <t>1820765</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>50,24%</t>
+          <t>47,31%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>46,45%</t>
+          <t>45,84%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>59,27%</t>
+          <t>48,86%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3862,32 +3862,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>3334382</t>
+          <t>3377832</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>3023394</t>
+          <t>3287379</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>3656725</t>
+          <t>3460626</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>46,9%</t>
+          <t>46,56%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>42,53%</t>
+          <t>45,31%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>51,44%</t>
+          <t>47,7%</t>
         </is>
       </c>
     </row>
@@ -3905,32 +3905,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>1547522</t>
+          <t>1460664</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>1379554</t>
+          <t>1391715</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>2002004</t>
+          <t>1529256</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>44,78%</t>
+          <t>41,39%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>39,92%</t>
+          <t>39,44%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>57,93%</t>
+          <t>43,33%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3940,32 +3940,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>1242062</t>
+          <t>1318280</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>1055393</t>
+          <t>1265172</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>1382655</t>
+          <t>1370305</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>34,0%</t>
+          <t>35,38%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>28,89%</t>
+          <t>33,95%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>37,85%</t>
+          <t>36,78%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3975,32 +3975,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>2789584</t>
+          <t>2778945</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>2528757</t>
+          <t>2698007</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>3237245</t>
+          <t>2867238</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>39,24%</t>
+          <t>38,3%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>35,57%</t>
+          <t>37,19%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>45,54%</t>
+          <t>39,52%</t>
         </is>
       </c>
     </row>
@@ -4018,17 +4018,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>3455954</t>
+          <t>3528958</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>3455954</t>
+          <t>3528958</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>3455954</t>
+          <t>3528958</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4053,17 +4053,17 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>3653401</t>
+          <t>3726155</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>3653401</t>
+          <t>3726155</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>3653401</t>
+          <t>3726155</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4088,17 +4088,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>7109355</t>
+          <t>7255114</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>7109355</t>
+          <t>7255114</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>7109355</t>
+          <t>7255114</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
